--- a/exports/exhibit-top-50.xlsx
+++ b/exports/exhibit-top-50.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Top 50 Most-Articulated Exhibit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 50 Most-Articulated Exhibit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/exhibit-top-50.xlsx
+++ b/exports/exhibit-top-50.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 50 Most-Articulated Exhibit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Top 50 Most-Articulated Exhibit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,7 +627,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AP Physics C: Mechanics (score 3-5): Cal-GETC Area 5A and 5C</t>
+          <t>AP Physics C: Electricity/Magnetism (score 3-5): Cal-GETC Area 5A and 5C</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AP Physics C: Electricity/Magnetism (score 3-5): Cal-GETC Area 5A and 5C</t>
+          <t>AP Physics C: Mechanics (score 3-5): Cal-GETC Area 5A and 5C</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Foreign Languages</t>
+          <t>Architecture and Related Technologies</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Interdisciplinary Studies</t>
+          <t>Psychology</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AP European History (score 3-5): Cal-GETC Area 3B or 4</t>
+          <t>AP U.S. History (score 3-5): Cal-GETC Area 3B or 4</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Social Sciences</t>
+          <t>Interdisciplinary Studies</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AP U.S. History (score 3-5): Cal-GETC Area 3B or 4</t>
+          <t>AP World History: Modern (score 3-5): Cal-GETC Area 3B or 4</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Social Sciences</t>
+          <t>Interdisciplinary Studies</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AP World History: Modern (score 3-5): Cal-GETC Area 3B or 4</t>
+          <t>AP European History (score 3-5): Cal-GETC Area 3B or 4</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Social Sciences</t>
+          <t>Interdisciplinary Studies</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Social Sciences</t>
+          <t>Interdisciplinary Studies</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AP Calculus BC (score 3-5): Cal-GETC Area 2</t>
+          <t>AP Calculus BC/ AB sub score (score 3-5): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AP Calculus BC/ AB sub score (score 3-5): Cal-GETC Area 2</t>
+          <t>AP Calculus BC (score 3-5): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AP Comparative Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
+          <t>AP French Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AP French Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Comparative Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AP Japanese Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Latin (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AP Latin (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Macroeconomics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AP Macroeconomics (score 3-5): Cal-GETC Area 4</t>
+          <t>AP Microeconomics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AP Microeconomics (score 3-5): Cal-GETC Area 4</t>
+          <t>AP Spanish Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AP Spanish Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Spanish Literature &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AP Spanish Literature &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Statistics (score 3-5): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AP Statistics (score 3-5): Cal-GETC Area 2</t>
+          <t>IB Economics HL (score 5-7): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AP U.S. Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
+          <t>IB Language A: Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AP Art History (score 3-5): Cal-GETC Area 3A or 3B</t>
+          <t>IB Geography HL (score 5-7): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IB Biology HL (score 5-7): Cal-GETC Area 5B</t>
+          <t>AP Japanese Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IB Chemistry HL (score 5-7): Cal-GETC Area 5A</t>
+          <t>IB Language A: Language and Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IB Economics HL (score 5-7): Cal-GETC Area 4</t>
+          <t>AP U.S. Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IB Geography HL (score 5-7): Cal-GETC Area 4</t>
+          <t>IB Language A: Language and Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IB Language A: Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>IB Biology HL (score 5-7): Cal-GETC Area 5B</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IB Language A: Language and Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>IB Language A: Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IB Language A: Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>IB Chemistry HL (score 5-7): Cal-GETC Area 5A</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IB Language A: Language and Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>IB Mathematics: Analysis and Approaches HL (score 5-7): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IB Mathematics: Analysis and Approaches HL (score 5-7): Cal-GETC Area 2</t>
+          <t>IB Mathematics: Applications and Interpretation HL (score 5-7): Cal-GETC Area 2 (may not be at all UC)</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IB Mathematics: Applications and Interpretation HL (score 5-7): Cal-GETC Area 2 (may not be at all UC)</t>
+          <t>IB Psychology HL (score 5-7): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IB Psychology HL (score 5-7): Cal-GETC Area 4</t>
+          <t>AP English Literature/Composition (score 3-5): Cal-GETC Area 1A or 3B</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AP English Literature/Composition (score 3-5): Cal-GETC Area 1A or 3B</t>
+          <t>AP Art History (score 3-5): Cal-GETC Area 3A or 3B</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D49" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Business and Management</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Engineering and Industrial Technologies</t>
+          <t>Family and Consumer Sciences</t>
         </is>
       </c>
     </row>

--- a/exports/exhibit-top-50.xlsx
+++ b/exports/exhibit-top-50.xlsx
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,7 +627,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AP Physics C: Electricity/Magnetism (score 3-5): Cal-GETC Area 5A and 5C</t>
+          <t>AP Physics C: Mechanics (score 3-5): Cal-GETC Area 5A and 5C</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AP Physics C: Mechanics (score 3-5): Cal-GETC Area 5A and 5C</t>
+          <t>AP Physics C: Electricity/Magnetism (score 3-5): Cal-GETC Area 5A and 5C</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Architecture and Related Technologies</t>
+          <t>Foreign Languages</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Interdisciplinary Studies</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AP U.S. History (score 3-5): Cal-GETC Area 3B or 4</t>
+          <t>AP European History (score 3-5): Cal-GETC Area 3B or 4</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Interdisciplinary Studies</t>
+          <t>Social Sciences</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AP World History: Modern (score 3-5): Cal-GETC Area 3B or 4</t>
+          <t>AP U.S. History (score 3-5): Cal-GETC Area 3B or 4</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Interdisciplinary Studies</t>
+          <t>Social Sciences</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AP European History (score 3-5): Cal-GETC Area 3B or 4</t>
+          <t>AP World History: Modern (score 3-5): Cal-GETC Area 3B or 4</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Interdisciplinary Studies</t>
+          <t>Social Sciences</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Interdisciplinary Studies</t>
+          <t>Social Sciences</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AP Calculus BC/ AB sub score (score 3-5): Cal-GETC Area 2</t>
+          <t>AP Calculus BC (score 3-5): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AP Calculus BC (score 3-5): Cal-GETC Area 2</t>
+          <t>AP Calculus BC/ AB sub score (score 3-5): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AP French Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Comparative Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AP Comparative Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
+          <t>AP French Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AP Latin (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Japanese Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AP Macroeconomics (score 3-5): Cal-GETC Area 4</t>
+          <t>AP Latin (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AP Microeconomics (score 3-5): Cal-GETC Area 4</t>
+          <t>AP Macroeconomics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AP Spanish Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Microeconomics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AP Spanish Literature &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>AP Spanish Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AP Statistics (score 3-5): Cal-GETC Area 2</t>
+          <t>AP Spanish Literature &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IB Economics HL (score 5-7): Cal-GETC Area 4</t>
+          <t>AP Statistics (score 3-5): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IB Language A: Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>AP U.S. Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IB Geography HL (score 5-7): Cal-GETC Area 4</t>
+          <t>AP Art History (score 3-5): Cal-GETC Area 3A or 3B</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AP Japanese Language &amp; Culture (score 3-5): Cal-GETC Area 3B</t>
+          <t>IB Biology HL (score 5-7): Cal-GETC Area 5B</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IB Language A: Language and Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>IB Chemistry HL (score 5-7): Cal-GETC Area 5A</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AP U.S. Government &amp; Politics (score 3-5): Cal-GETC Area 4</t>
+          <t>IB Economics HL (score 5-7): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IB Language A: Language and Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>IB Geography HL (score 5-7): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IB Biology HL (score 5-7): Cal-GETC Area 5B</t>
+          <t>IB Language A: Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IB Language A: Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
+          <t>IB Language A: Language and Literature (any language, except English) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IB Chemistry HL (score 5-7): Cal-GETC Area 5A</t>
+          <t>IB Language A: Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IB Mathematics: Analysis and Approaches HL (score 5-7): Cal-GETC Area 2</t>
+          <t>IB Language A: Language and Literature (any language) HL (score 5-7): Cal-GETC Area 3B</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IB Mathematics: Applications and Interpretation HL (score 5-7): Cal-GETC Area 2 (may not be at all UC)</t>
+          <t>IB Mathematics: Analysis and Approaches HL (score 5-7): Cal-GETC Area 2</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IB Psychology HL (score 5-7): Cal-GETC Area 4</t>
+          <t>IB Mathematics: Applications and Interpretation HL (score 5-7): Cal-GETC Area 2 (may not be at all UC)</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AP English Literature/Composition (score 3-5): Cal-GETC Area 1A or 3B</t>
+          <t>IB Psychology HL (score 5-7): Cal-GETC Area 4</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AP Art History (score 3-5): Cal-GETC Area 3A or 3B</t>
+          <t>AP English Literature/Composition (score 3-5): Cal-GETC Area 1A or 3B</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Business and Management</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Family and Consumer Sciences</t>
+          <t>Engineering and Industrial Technologies</t>
         </is>
       </c>
     </row>
